--- a/static/data/exports/Retro_NL_GE_2024.xlsx
+++ b/static/data/exports/Retro_NL_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8851,20 +8851,20 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1948834</v>
+        <v>1948833</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="Q162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" t="n">
         <v>53</v>
@@ -8903,20 +8903,20 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1948835</v>
+        <v>1948834</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -8955,20 +8955,20 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1948833</v>
+        <v>1948835</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Q164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>53</v>
@@ -9163,20 +9163,20 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1948840</v>
+        <v>1948839</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="Q168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
         <v>53</v>
@@ -9215,20 +9215,20 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1948841</v>
+        <v>1948840</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -9267,20 +9267,20 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1948839</v>
+        <v>1948841</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -9303,7 +9303,7 @@
         </is>
       </c>
       <c r="Q170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>53</v>
@@ -9319,20 +9319,20 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1948843</v>
+        <v>1948844</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -9371,20 +9371,20 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1948844</v>
+        <v>1948842</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Q172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" t="n">
         <v>53</v>
@@ -9423,20 +9423,20 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1948842</v>
+        <v>1948843</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="Q173" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>53</v>
@@ -9475,20 +9475,20 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1948846</v>
+        <v>1948847</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -9527,20 +9527,20 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1948847</v>
+        <v>1948845</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -9563,7 +9563,7 @@
         </is>
       </c>
       <c r="Q175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R175" t="n">
         <v>53</v>
@@ -9579,20 +9579,20 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1948845</v>
+        <v>1948846</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -9615,7 +9615,7 @@
         </is>
       </c>
       <c r="Q176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>53</v>
@@ -9631,20 +9631,20 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1948849</v>
+        <v>1948848</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="Q177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R177" t="n">
         <v>53</v>
@@ -9735,20 +9735,20 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1948848</v>
+        <v>1948849</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -9771,7 +9771,7 @@
         </is>
       </c>
       <c r="Q179" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>53</v>
@@ -9787,20 +9787,20 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1948852</v>
+        <v>1948851</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         </is>
       </c>
       <c r="Q180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R180" t="n">
         <v>53</v>
@@ -9839,20 +9839,20 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1948853</v>
+        <v>1948852</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -9891,20 +9891,20 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1948851</v>
+        <v>1948853</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="Q182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>53</v>
@@ -9943,20 +9943,20 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1948855</v>
+        <v>1948856</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
@@ -9995,20 +9995,20 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1948856</v>
+        <v>1948854</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -10031,7 +10031,7 @@
         </is>
       </c>
       <c r="Q184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R184" t="n">
         <v>53</v>
@@ -10047,20 +10047,20 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1948854</v>
+        <v>1948855</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -10083,7 +10083,7 @@
         </is>
       </c>
       <c r="Q185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>53</v>
@@ -10099,20 +10099,20 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1948858</v>
+        <v>1948857</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="Q186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186" t="n">
         <v>53</v>
@@ -10151,20 +10151,20 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1948859</v>
+        <v>1948858</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -10203,20 +10203,20 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1948857</v>
+        <v>1948859</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="Q188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
         <v>53</v>
@@ -10619,20 +10619,20 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1948868</v>
+        <v>1948866</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         </is>
       </c>
       <c r="Q196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R196" t="n">
         <v>53</v>
@@ -10671,20 +10671,20 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1948866</v>
+        <v>1948868</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -10707,7 +10707,7 @@
         </is>
       </c>
       <c r="Q197" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>53</v>
@@ -10775,20 +10775,20 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1948871</v>
+        <v>1948869</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="Q199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" t="n">
         <v>53</v>
@@ -10827,20 +10827,20 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1948869</v>
+        <v>1948871</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="Q200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>53</v>
@@ -10879,20 +10879,20 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1948873</v>
+        <v>1948872</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="Q201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R201" t="n">
         <v>53</v>
@@ -10931,20 +10931,20 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1948874</v>
+        <v>1948873</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -10983,20 +10983,20 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1948872</v>
+        <v>1948874</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -11019,7 +11019,7 @@
         </is>
       </c>
       <c r="Q203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>53</v>
@@ -11035,20 +11035,20 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1948876</v>
+        <v>1948877</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -11087,20 +11087,20 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1948877</v>
+        <v>1948875</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -11123,7 +11123,7 @@
         </is>
       </c>
       <c r="Q205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R205" t="n">
         <v>53</v>
@@ -11139,20 +11139,20 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1948875</v>
+        <v>1948876</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -11175,7 +11175,7 @@
         </is>
       </c>
       <c r="Q206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>53</v>
@@ -11191,20 +11191,20 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1948879</v>
+        <v>1948880</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -11243,20 +11243,20 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1948880</v>
+        <v>1948878</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         </is>
       </c>
       <c r="Q208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R208" t="n">
         <v>53</v>
@@ -11295,20 +11295,20 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1948878</v>
+        <v>1948879</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         </is>
       </c>
       <c r="Q209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R209" t="n">
         <v>53</v>
@@ -11399,20 +11399,20 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1948883</v>
+        <v>1948881</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="Q211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R211" t="n">
         <v>53</v>
@@ -11451,20 +11451,20 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1948881</v>
+        <v>1948883</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -11487,7 +11487,7 @@
         </is>
       </c>
       <c r="Q212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>53</v>
@@ -11503,20 +11503,20 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1948885</v>
+        <v>1948884</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="Q213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R213" t="n">
         <v>53</v>
@@ -11607,20 +11607,20 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1948884</v>
+        <v>1948885</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -11643,7 +11643,7 @@
         </is>
       </c>
       <c r="Q215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>53</v>
@@ -11659,20 +11659,20 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1948888</v>
+        <v>1948887</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>26925</v>
+        <v>26926</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         </is>
       </c>
       <c r="Q216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
         <v>53</v>
@@ -11711,20 +11711,20 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1948889</v>
+        <v>1948888</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>26927</v>
+        <v>26925</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -11763,20 +11763,20 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1948887</v>
+        <v>1948889</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>26926</v>
+        <v>26927</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -11799,7 +11799,7 @@
         </is>
       </c>
       <c r="Q218" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>53</v>
@@ -11815,20 +11815,20 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1948891</v>
+        <v>1948892</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>S Supongmeren Jamir</t>
+          <t>Hayithung Tungoe Lotha</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>INC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>26925</v>
+        <v>26927</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
@@ -11867,20 +11867,20 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1948892</v>
+        <v>1948890</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Hayithung Tungoe Lotha</t>
+          <t>Dr Chumben Murry</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NDPP</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>26927</v>
+        <v>26926</v>
       </c>
       <c r="E220" t="n">
         <v>0</v>
@@ -11903,7 +11903,7 @@
         </is>
       </c>
       <c r="Q220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
         <v>53</v>
@@ -11919,20 +11919,20 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1948890</v>
+        <v>1948891</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dr Chumben Murry</t>
+          <t>S Supongmeren Jamir</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>NDPP</t>
+          <t>INC</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>26926</v>
+        <v>26925</v>
       </c>
       <c r="E221" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         </is>
       </c>
       <c r="Q221" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>53</v>
